--- a/data/availability/projects/al-marasem-developments/marresidence.xlsx
+++ b/data/availability/projects/al-marasem-developments/marresidence.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Serviced Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Serviced Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -785,7 +785,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Serviced Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Serviced Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
